--- a/artfynd/A 17230-2026 artfynd.xlsx
+++ b/artfynd/A 17230-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131752894</v>
+        <v>133118496</v>
       </c>
       <c r="B2" t="n">
-        <v>57948</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norderåssjön, Jmt</t>
+          <t>Messmörhålet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496473</v>
+        <v>496451</v>
       </c>
       <c r="R2" t="n">
-        <v>7036447</v>
+        <v>7036450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,17 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Flera fruktkroppar i stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,14 +785,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,53 +805,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131752895</v>
+        <v>133118494</v>
       </c>
       <c r="B3" t="n">
-        <v>57948</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norderåssjön, Jmt</t>
+          <t>Messmörhålet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496454</v>
+        <v>496509</v>
       </c>
       <c r="R3" t="n">
-        <v>7036472</v>
+        <v>7036448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,17 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,32 +888,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,37 +912,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133118519</v>
+        <v>133118495</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496333</v>
+        <v>496620</v>
       </c>
       <c r="R4" t="n">
-        <v>7036351</v>
+        <v>7036522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,11 +989,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,26 +1002,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,14 +1019,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133118509</v>
+        <v>133118497</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1114,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496648</v>
+        <v>496474</v>
       </c>
       <c r="R5" t="n">
-        <v>7036551</v>
+        <v>7036350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,11 +1093,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1202,14 +1140,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133118501</v>
+        <v>133118498</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1240,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496511</v>
+        <v>496486</v>
       </c>
       <c r="R6" t="n">
-        <v>7036415</v>
+        <v>7036381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,11 +1216,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1308,14 +1241,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1333,14 +1261,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133118516</v>
+        <v>133118499</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1371,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496453</v>
+        <v>496503</v>
       </c>
       <c r="R7" t="n">
-        <v>7036330</v>
+        <v>7036398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,6 +1337,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1434,9 +1367,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1454,14 +1392,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133118507</v>
+        <v>133118500</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1492,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496540</v>
+        <v>496546</v>
       </c>
       <c r="R8" t="n">
-        <v>7036518</v>
+        <v>7036437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1575,14 +1513,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133118500</v>
+        <v>133118501</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1613,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496546</v>
+        <v>496511</v>
       </c>
       <c r="R9" t="n">
-        <v>7036437</v>
+        <v>7036415</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1651,6 +1589,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1676,9 +1619,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,14 +1644,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133118498</v>
+        <v>133118502</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1734,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496486</v>
+        <v>496564</v>
       </c>
       <c r="R10" t="n">
-        <v>7036381</v>
+        <v>7036463</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1772,6 +1720,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1797,9 +1750,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1820,11 +1778,11 @@
         <v>133118503</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1943,14 +1901,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133118497</v>
+        <v>133118504</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1981,10 +1939,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496474</v>
+        <v>496453</v>
       </c>
       <c r="R12" t="n">
-        <v>7036350</v>
+        <v>7036464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,14 +2022,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133118512</v>
+        <v>133118505</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2102,10 +2060,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496369</v>
+        <v>496461</v>
       </c>
       <c r="R13" t="n">
-        <v>7036366</v>
+        <v>7036468</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,6 +2098,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2165,9 +2128,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2185,14 +2153,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133118518</v>
+        <v>133118506</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2223,10 +2191,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496363</v>
+        <v>496480</v>
       </c>
       <c r="R14" t="n">
-        <v>7036333</v>
+        <v>7036488</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2263,7 +2231,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På grenar av en stående död gran.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,14 +2259,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2316,41 +2279,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133118496</v>
+        <v>133118507</v>
       </c>
       <c r="B15" t="n">
-        <v>91924</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2358,10 +2317,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496451</v>
+        <v>496540</v>
       </c>
       <c r="R15" t="n">
-        <v>7036450</v>
+        <v>7036518</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2394,11 +2353,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2446,14 +2400,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133118510</v>
+        <v>133118508</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2484,10 +2438,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496672</v>
+        <v>496619</v>
       </c>
       <c r="R16" t="n">
-        <v>7036551</v>
+        <v>7036511</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2520,11 +2474,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2572,14 +2521,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133118508</v>
+        <v>133118509</v>
       </c>
       <c r="B17" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2610,10 +2559,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496619</v>
+        <v>496648</v>
       </c>
       <c r="R17" t="n">
-        <v>7036511</v>
+        <v>7036551</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2646,6 +2595,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2693,14 +2647,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133118505</v>
+        <v>133118510</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2731,10 +2685,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496461</v>
+        <v>496672</v>
       </c>
       <c r="R18" t="n">
-        <v>7036468</v>
+        <v>7036551</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2771,7 +2725,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2799,14 +2753,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2824,14 +2773,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133118513</v>
+        <v>133118511</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2862,10 +2811,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496448</v>
+        <v>496528</v>
       </c>
       <c r="R19" t="n">
-        <v>7036373</v>
+        <v>7036529</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2900,6 +2849,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2925,9 +2879,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2945,14 +2904,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133118502</v>
+        <v>133118512</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2983,10 +2942,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496564</v>
+        <v>496369</v>
       </c>
       <c r="R20" t="n">
-        <v>7036463</v>
+        <v>7036366</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3021,11 +2980,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3051,14 +3005,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3076,65 +3025,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133118493</v>
+        <v>133118513</v>
       </c>
       <c r="B21" t="n">
-        <v>58332</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Messmörhålet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496582</v>
+        <v>496448</v>
       </c>
       <c r="R21" t="n">
-        <v>7036499</v>
+        <v>7036373</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3169,23 +3101,34 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>1 ex med sång.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3203,14 +3146,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133118504</v>
+        <v>133118514</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3241,10 +3184,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496453</v>
+        <v>496397</v>
       </c>
       <c r="R22" t="n">
-        <v>7036464</v>
+        <v>7036397</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3279,6 +3222,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gren av en grov gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3304,9 +3252,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3324,61 +3277,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133118456</v>
+        <v>133118515</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Messmörhålet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496598</v>
+        <v>496452</v>
       </c>
       <c r="R23" t="n">
-        <v>7036520</v>
+        <v>7036395</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3415,7 +3355,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Gammalt bohål, 2 st på 1,2 m höjd respektive 2 m höjd med 40-45 mm i diameter, i en stående död gran med full längd och 21 cm i brösthöjdsdiameter. På/kring fyndplatsen finns stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3424,6 +3364,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3442,14 +3383,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3467,14 +3403,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133118515</v>
+        <v>133118516</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3505,10 +3441,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496452</v>
+        <v>496453</v>
       </c>
       <c r="R24" t="n">
-        <v>7036395</v>
+        <v>7036330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3541,11 +3477,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3593,14 +3524,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133118511</v>
+        <v>133118517</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3631,10 +3562,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496528</v>
+        <v>496438</v>
       </c>
       <c r="R25" t="n">
-        <v>7036529</v>
+        <v>7036349</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3671,7 +3602,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På grenar av en stående död gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3699,14 +3630,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3724,14 +3650,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133118506</v>
+        <v>133118518</v>
       </c>
       <c r="B26" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3762,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496480</v>
+        <v>496363</v>
       </c>
       <c r="R26" t="n">
-        <v>7036488</v>
+        <v>7036333</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3802,7 +3728,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>På grenar av en stående död gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3830,9 +3756,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3850,32 +3781,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133118488</v>
+        <v>133118519</v>
       </c>
       <c r="B27" t="n">
-        <v>80467</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3888,10 +3819,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496401</v>
+        <v>496333</v>
       </c>
       <c r="R27" t="n">
-        <v>7036334</v>
+        <v>7036351</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3926,6 +3857,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3941,9 +3877,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av tall.</t>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3961,32 +3912,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133118514</v>
+        <v>133118488</v>
       </c>
       <c r="B28" t="n">
-        <v>79334</v>
+        <v>80492</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3999,10 +3950,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496397</v>
+        <v>496401</v>
       </c>
       <c r="R28" t="n">
-        <v>7036397</v>
+        <v>7036334</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4037,11 +3988,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gren av en grov gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4057,24 +4003,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av tall.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4092,10 +4023,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133118517</v>
+        <v>131752892</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4103,37 +4034,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Messmörhålet, Jmt</t>
+          <t>Norderåssjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496438</v>
+        <v>496363</v>
       </c>
       <c r="R29" t="n">
-        <v>7036349</v>
+        <v>7036414</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4160,17 +4096,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4179,7 +4115,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4198,9 +4133,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4218,10 +4158,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133118499</v>
+        <v>131752893</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4229,37 +4169,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Messmörhålet, Jmt</t>
+          <t>Norderåssjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496503</v>
+        <v>496357</v>
       </c>
       <c r="R30" t="n">
-        <v>7036398</v>
+        <v>7036419</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4286,17 +4231,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4305,7 +4250,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4326,12 +4270,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4349,49 +4293,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133118487</v>
+        <v>131752894</v>
       </c>
       <c r="B31" t="n">
-        <v>98005</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Messmörhålet, Jmt</t>
+          <t>Norderåssjön, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496447</v>
+        <v>496473</v>
       </c>
       <c r="R31" t="n">
-        <v>7036389</v>
+        <v>7036447</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4418,12 +4366,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4432,13 +4385,32 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4456,10 +4428,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133118467</v>
+        <v>131752895</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4495,14 +4467,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Messmörhålet, Jmt</t>
+          <t>Norderåssjön, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496341</v>
+        <v>496454</v>
       </c>
       <c r="R32" t="n">
-        <v>7036366</v>
+        <v>7036472</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4529,17 +4501,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, högt upp på en grov gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4591,7 +4563,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133118458</v>
+        <v>133118450</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -4624,7 +4596,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4634,10 +4606,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496400</v>
+        <v>496505</v>
       </c>
       <c r="R33" t="n">
-        <v>7036441</v>
+        <v>7036415</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4674,7 +4646,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4701,14 +4673,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4726,7 +4693,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133118471</v>
+        <v>133118451</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -4759,7 +4726,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4769,10 +4736,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496444</v>
+        <v>496543</v>
       </c>
       <c r="R34" t="n">
-        <v>7036331</v>
+        <v>7036433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4809,7 +4776,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, högt upp på en gran.</t>
+          <t>Ringhack, äldre, med kådaflöden på en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4836,14 +4803,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4861,7 +4823,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133118455</v>
+        <v>133118452</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4904,10 +4866,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496573</v>
+        <v>496531</v>
       </c>
       <c r="R35" t="n">
-        <v>7036511</v>
+        <v>7036454</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4944,7 +4906,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4971,14 +4933,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4996,7 +4953,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133118466</v>
+        <v>133118453</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -5039,10 +4996,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496338</v>
+        <v>496514</v>
       </c>
       <c r="R36" t="n">
-        <v>7036363</v>
+        <v>7036493</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5079,7 +5036,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5108,12 +5065,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5131,7 +5088,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133118472</v>
+        <v>133118454</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -5164,7 +5121,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5174,10 +5131,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496435</v>
+        <v>496573</v>
       </c>
       <c r="R37" t="n">
-        <v>7036334</v>
+        <v>7036510</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5214,7 +5171,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, högt upp på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5266,7 +5223,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133118451</v>
+        <v>133118455</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -5309,10 +5266,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496543</v>
+        <v>496573</v>
       </c>
       <c r="R38" t="n">
-        <v>7036433</v>
+        <v>7036511</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5349,7 +5306,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, med kådaflöden på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran. På fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5376,9 +5333,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5396,7 +5358,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133118483</v>
+        <v>133118456</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -5424,25 +5386,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Messmörhålet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496357</v>
+        <v>496598</v>
       </c>
       <c r="R39" t="n">
-        <v>7036334</v>
+        <v>7036520</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5479,7 +5449,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Gammalt bohål, 2 st på 1,2 m höjd respektive 2 m höjd med 40-45 mm i diameter, i en stående död gran med full längd och 21 cm i brösthöjdsdiameter. På/kring fyndplatsen finns stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5508,12 +5478,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5531,7 +5501,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133118481</v>
+        <v>133118457</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -5564,7 +5534,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5574,10 +5544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496386</v>
+        <v>496422</v>
       </c>
       <c r="R40" t="n">
-        <v>7036331</v>
+        <v>7036484</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5614,7 +5584,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran med rikligt med kådaflöden.</t>
+          <t>Ringhack (savhack), färska, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5666,7 +5636,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133118463</v>
+        <v>133118458</v>
       </c>
       <c r="B41" t="n">
         <v>57975</v>
@@ -5709,10 +5679,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496378</v>
+        <v>496400</v>
       </c>
       <c r="R41" t="n">
-        <v>7036416</v>
+        <v>7036441</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5801,7 +5771,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133118479</v>
+        <v>133118459</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -5844,10 +5814,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496403</v>
+        <v>496395</v>
       </c>
       <c r="R42" t="n">
-        <v>7036332</v>
+        <v>7036438</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5884,7 +5854,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, långt upp på en grov gran.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5936,7 +5906,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133118484</v>
+        <v>133118460</v>
       </c>
       <c r="B43" t="n">
         <v>57975</v>
@@ -5979,10 +5949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496356</v>
+        <v>496394</v>
       </c>
       <c r="R43" t="n">
-        <v>7036333</v>
+        <v>7036435</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6019,7 +5989,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran.</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6071,7 +6041,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133118473</v>
+        <v>133118461</v>
       </c>
       <c r="B44" t="n">
         <v>57975</v>
@@ -6114,10 +6084,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496436</v>
+        <v>496383</v>
       </c>
       <c r="R44" t="n">
-        <v>7036331</v>
+        <v>7036419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6154,7 +6124,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack, färska, tydliga på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6206,7 +6176,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133118470</v>
+        <v>133118462</v>
       </c>
       <c r="B45" t="n">
         <v>57975</v>
@@ -6249,10 +6219,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496452</v>
+        <v>496380</v>
       </c>
       <c r="R45" t="n">
-        <v>7036325</v>
+        <v>7036417</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6341,7 +6311,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133118450</v>
+        <v>133118463</v>
       </c>
       <c r="B46" t="n">
         <v>57975</v>
@@ -6374,7 +6344,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6384,10 +6354,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496505</v>
+        <v>496378</v>
       </c>
       <c r="R46" t="n">
-        <v>7036415</v>
+        <v>7036416</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6424,7 +6394,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6451,9 +6421,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6471,7 +6446,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133118480</v>
+        <v>133118464</v>
       </c>
       <c r="B47" t="n">
         <v>57975</v>
@@ -6514,10 +6489,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496394</v>
+        <v>496369</v>
       </c>
       <c r="R47" t="n">
-        <v>7036329</v>
+        <v>7036404</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6554,7 +6529,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en klen gran.</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6606,7 +6581,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133118468</v>
+        <v>133118465</v>
       </c>
       <c r="B48" t="n">
         <v>57975</v>
@@ -6639,7 +6614,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6649,10 +6624,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496469</v>
+        <v>496331</v>
       </c>
       <c r="R48" t="n">
-        <v>7036349</v>
+        <v>7036354</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6689,7 +6664,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en klen gran.</t>
+          <t>Ringhack (savhack), färska och äldre, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6716,9 +6691,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6736,7 +6716,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133118465</v>
+        <v>133118466</v>
       </c>
       <c r="B49" t="n">
         <v>57975</v>
@@ -6769,7 +6749,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6779,10 +6759,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496331</v>
+        <v>496338</v>
       </c>
       <c r="R49" t="n">
-        <v>7036354</v>
+        <v>7036363</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6819,7 +6799,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, högt upp på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6871,7 +6851,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133118460</v>
+        <v>133118467</v>
       </c>
       <c r="B50" t="n">
         <v>57975</v>
@@ -6914,10 +6894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496394</v>
+        <v>496341</v>
       </c>
       <c r="R50" t="n">
-        <v>7036435</v>
+        <v>7036366</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6954,7 +6934,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, högt upp på en grov gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7006,7 +6986,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133118477</v>
+        <v>133118468</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -7049,10 +7029,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496423</v>
+        <v>496469</v>
       </c>
       <c r="R51" t="n">
-        <v>7036332</v>
+        <v>7036349</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7089,7 +7069,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en klen gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7116,14 +7096,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7141,7 +7116,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133118453</v>
+        <v>133118469</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -7184,10 +7159,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496514</v>
+        <v>496468</v>
       </c>
       <c r="R52" t="n">
-        <v>7036493</v>
+        <v>7036348</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7224,7 +7199,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7251,14 +7226,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7276,7 +7246,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133118462</v>
+        <v>133118470</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -7319,10 +7289,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496380</v>
+        <v>496452</v>
       </c>
       <c r="R53" t="n">
-        <v>7036417</v>
+        <v>7036325</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7411,7 +7381,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133118475</v>
+        <v>133118471</v>
       </c>
       <c r="B54" t="n">
         <v>57975</v>
@@ -7454,10 +7424,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496429</v>
+        <v>496444</v>
       </c>
       <c r="R54" t="n">
-        <v>7036330</v>
+        <v>7036331</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7494,7 +7464,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7546,7 +7516,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133118469</v>
+        <v>133118472</v>
       </c>
       <c r="B55" t="n">
         <v>57975</v>
@@ -7579,7 +7549,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7589,10 +7559,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496468</v>
+        <v>496435</v>
       </c>
       <c r="R55" t="n">
-        <v>7036348</v>
+        <v>7036334</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7629,7 +7599,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7656,9 +7626,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7676,7 +7651,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133118454</v>
+        <v>133118473</v>
       </c>
       <c r="B56" t="n">
         <v>57975</v>
@@ -7709,7 +7684,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7719,10 +7694,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496573</v>
+        <v>496436</v>
       </c>
       <c r="R56" t="n">
-        <v>7036510</v>
+        <v>7036331</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7759,7 +7734,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7811,7 +7786,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133118464</v>
+        <v>133118474</v>
       </c>
       <c r="B57" t="n">
         <v>57975</v>
@@ -7854,10 +7829,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496369</v>
+        <v>496430</v>
       </c>
       <c r="R57" t="n">
-        <v>7036404</v>
+        <v>7036325</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7946,7 +7921,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133118461</v>
+        <v>133118475</v>
       </c>
       <c r="B58" t="n">
         <v>57975</v>
@@ -7989,10 +7964,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496383</v>
+        <v>496429</v>
       </c>
       <c r="R58" t="n">
-        <v>7036419</v>
+        <v>7036330</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8029,7 +8004,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska, tydliga på stambasen av en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8081,7 +8056,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133118474</v>
+        <v>133118476</v>
       </c>
       <c r="B59" t="n">
         <v>57975</v>
@@ -8114,7 +8089,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8124,7 +8099,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496430</v>
+        <v>496425</v>
       </c>
       <c r="R59" t="n">
         <v>7036325</v>
@@ -8164,7 +8139,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran med rikligt kådaflöde.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8191,14 +8166,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8216,7 +8186,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133118459</v>
+        <v>133118477</v>
       </c>
       <c r="B60" t="n">
         <v>57975</v>
@@ -8249,7 +8219,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8259,10 +8229,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496395</v>
+        <v>496423</v>
       </c>
       <c r="R60" t="n">
-        <v>7036438</v>
+        <v>7036332</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8299,7 +8269,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8351,7 +8321,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133118485</v>
+        <v>133118478</v>
       </c>
       <c r="B61" t="n">
         <v>57975</v>
@@ -8394,10 +8364,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496337</v>
+        <v>496417</v>
       </c>
       <c r="R61" t="n">
-        <v>7036337</v>
+        <v>7036328</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8434,7 +8404,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8486,7 +8456,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133118482</v>
+        <v>133118479</v>
       </c>
       <c r="B62" t="n">
         <v>57975</v>
@@ -8529,7 +8499,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496376</v>
+        <v>496403</v>
       </c>
       <c r="R62" t="n">
         <v>7036332</v>
@@ -8569,7 +8539,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, högt upp på en gran. Högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Ringhack (savhack), färska, långt upp på en grov gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8621,7 +8591,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133118478</v>
+        <v>133118480</v>
       </c>
       <c r="B63" t="n">
         <v>57975</v>
@@ -8664,10 +8634,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496417</v>
+        <v>496394</v>
       </c>
       <c r="R63" t="n">
-        <v>7036328</v>
+        <v>7036329</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8704,7 +8674,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska, på en klen gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8756,7 +8726,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133118452</v>
+        <v>133118481</v>
       </c>
       <c r="B64" t="n">
         <v>57975</v>
@@ -8799,10 +8769,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496531</v>
+        <v>496386</v>
       </c>
       <c r="R64" t="n">
-        <v>7036454</v>
+        <v>7036331</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8839,7 +8809,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran med rikligt med kådaflöden.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8866,9 +8836,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8883,6 +8858,1224 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>133118482</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Messmörhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>496376</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7036332</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, högt upp på en gran. Högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>133118483</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Messmörhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>496357</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7036334</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>133118484</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Messmörhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>496356</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7036333</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>133118485</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Messmörhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>496337</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7036337</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>133118493</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Messmörhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>496582</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7036499</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>1 ex med sång.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>133118489</v>
+      </c>
+      <c r="B70" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Messmörhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>496501</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7036502</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>133118490</v>
+      </c>
+      <c r="B71" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Messmörhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>496406</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7036382</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>133118491</v>
+      </c>
+      <c r="B72" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Messmörhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>496426</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7036390</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>133118492</v>
+      </c>
+      <c r="B73" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Messmörhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>496408</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7036338</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>133118487</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Messmörhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>496447</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7036389</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17230-2026 artfynd.xlsx
+++ b/artfynd/A 17230-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118496</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118494</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118495</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118497</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118498</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118499</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1510,6 +1545,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118500</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1641,6 +1681,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118501</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1772,6 +1817,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118502</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1898,6 +1948,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118503</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2019,6 +2074,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118504</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2150,6 +2210,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118505</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2276,6 +2341,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118506</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2397,6 +2467,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118507</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2518,6 +2593,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118508</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2644,6 +2724,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118509</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2770,6 +2855,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118510</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2901,6 +2991,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118511</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3022,6 +3117,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118512</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3143,6 +3243,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118513</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3274,6 +3379,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118514</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3400,6 +3510,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118515</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3521,6 +3636,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118516</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3647,6 +3767,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118517</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3778,6 +3903,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118518</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3909,6 +4039,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118519</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4020,6 +4155,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118488</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4155,6 +4295,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131752892</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4290,6 +4435,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131752893</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4425,6 +4575,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131752894</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4560,6 +4715,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131752895</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4690,6 +4850,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118450</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4820,6 +4985,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118451</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4950,6 +5120,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118452</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5085,6 +5260,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118453</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5220,6 +5400,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118454</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5355,6 +5540,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118455</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5498,6 +5688,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118456</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5633,6 +5828,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118457</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5768,6 +5968,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118458</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5903,6 +6108,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118459</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6038,6 +6248,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118460</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6173,6 +6388,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118461</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6308,6 +6528,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118462</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6443,6 +6668,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118463</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6578,6 +6808,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118464</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6713,6 +6948,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118465</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6848,6 +7088,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118466</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6983,6 +7228,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118467</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7113,6 +7363,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118468</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7243,6 +7498,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118469</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7378,6 +7638,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118470</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7513,6 +7778,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118471</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7648,6 +7918,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118472</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7783,6 +8058,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118473</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7918,6 +8198,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118474</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8053,6 +8338,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118475</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8183,6 +8473,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118476</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8318,6 +8613,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118477</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8453,6 +8753,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118478</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8588,6 +8893,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118479</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8723,6 +9033,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118480</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8858,6 +9173,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118481</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8993,6 +9313,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118482</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9128,6 +9453,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118483</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9263,6 +9593,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118484</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9398,6 +9733,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118485</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9525,6 +9865,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118493</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9636,6 +9981,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118489</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9747,6 +10097,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118490</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9858,6 +10213,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118491</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9969,6 +10329,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118492</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10076,8 +10441,88 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133118487</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>